--- a/vd1.xlsx
+++ b/vd1.xlsx
@@ -14,66 +14,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Chư</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>ơng trình khung huần luyện nhóm Í</t>
-  </si>
-  <si>
-    <t>NỘI DUNG HUÁN LUYỆN</t>
-  </si>
-  <si>
-    <t>Hệ thống chính sách, pháp luật về an toàn, vệ sinh lao động</t>
-  </si>
-  <si>
-    <t>Tổng quan về hệ thông văn bản quy phạm     pháp luật về an toàn, vệ sinh lao động.</t>
-  </si>
-  <si>
-    <t>Hệ thống tiêu chuẩn, quy chuẩn kỹ thuật an     toàn, vệ sinh lao động.</t>
-  </si>
-  <si>
-    <t>Các quy định cụ thê của các cơ quan quản lý nhả nước về an toàn, vệ sinh lao động khi xây dựng mới, mở rộng hoặc cải tạo các công trình, các cơ sở để sản xuất, sử dụng, báo quản, lưu giữ và kiểm định các loại máy, thiết bị, vật tư,  các chât có yêu câu nghiêm ngặt về an toàn, vệ     sinh lao động.</t>
-  </si>
-  <si>
-    <t>Nghiệp vụ công tác an toàn, vệ sinh lao động</t>
-  </si>
-  <si>
-    <t>Tô chức bộ máy, quản lý và thực hiện các quy định về an toàn, vệ sinh lao động ở cơ sở; phân  định trách nhiệm và giao quyền hạn về công     tác an toàn, vệ sinh lao động.</t>
-  </si>
-  <si>
-    <t>Kiên thức cơ bản về các yếu tô nguy hiểm, có ại, biện pháp phòng ngừa.</t>
-  </si>
-  <si>
-    <t>Phương pháp cải thiện điều kiện lao động.</t>
-  </si>
-  <si>
-    <t>Văn hóa an toàn trong sản xuất, kinh doanh.</t>
-  </si>
-  <si>
-    <t>Kiểm tra kết thúc khóa huấn luyện</t>
-  </si>
-  <si>
-    <t>Tổng cộng</t>
-  </si>
-  <si>
-    <t>Thời  Tổng số</t>
-  </si>
-  <si>
-    <t>gian hui:  Lý thuyết</t>
-  </si>
-  <si>
-    <t>ìn luyện  Trong đ‹  Thực hành</t>
-  </si>
-  <si>
-    <t>(giờ)  Kiếm tra</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Mua sắm License OS Windows,Microsoft SQL Server</t>
+  </si>
+  <si>
+    <t>Mua sắm thiết bị Scan(theo tư vẫn cầu hình trên 2 loại máy của FujItsu và EPSON)</t>
+  </si>
+  <si>
+    <t>Cấp phát hạ tầng</t>
+  </si>
+  <si>
+    <t>Cài đặt triển khai hệ thống sau khi có License OS Windows,Microsoft SQL Server</t>
+  </si>
+  <si>
+    <t>Cài đặt, cầu hình chỉnh sửa CT đảm bảo an toàn bảo mật</t>
+  </si>
+  <si>
+    <t>Cấp phát IP Publie</t>
+  </si>
+  <si>
+    <t>Kiểm thử, đánh giá hệ thông</t>
+  </si>
+  <si>
+    <t>Chuẩn hóa dữ liệu, danh mục</t>
+  </si>
+  <si>
+    <t>Khai báo, cấu hình hệ thông</t>
+  </si>
+  <si>
+    <t>Cập nhật dữ liệu mẫu, kiêm thử</t>
+  </si>
+  <si>
+    <t>Tập huấn, chuyển giao hệ thông</t>
+  </si>
+  <si>
+    <t>Kiểm tra tổng thể hệ thông</t>
+  </si>
+  <si>
+    <t>Bản giao đưa vào sử dụng (thử nghiệm)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>LAR-</t>
+  </si>
+  <si>
+    <t>A/R</t>
+  </si>
+  <si>
+    <t>LAR,</t>
   </si>
 </sst>
 </file>
@@ -431,10 +437,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:12">
       <c r="B1" s="1">
         <v>0</v>
       </c>
@@ -456,8 +462,20 @@
       <c r="H1" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -465,121 +483,133 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
       <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>2</v>
       </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
       <c r="D4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="1">
         <v>6</v>
       </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
       <c r="D8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>11</v>
+      </c>
+      <c r="I8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>12</v>
+      </c>
+      <c r="J9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>14</v>
+      </c>
+      <c r="J11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="1">
         <v>10</v>
       </c>
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
       <c r="D12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
       <c r="D13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="1">
         <v>12</v>
       </c>
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
